--- a/artfynd/A 37417-2023 artfynd.xlsx
+++ b/artfynd/A 37417-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517882</v>
+        <v>123517878</v>
       </c>
       <c r="B2" t="n">
-        <v>100645</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637160</v>
+        <v>637093</v>
       </c>
       <c r="R2" t="n">
-        <v>6615284</v>
+        <v>6615299</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -780,7 +784,7 @@
         <v>123517839</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517878</v>
+        <v>123517868</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637093</v>
+        <v>637396</v>
       </c>
       <c r="R4" t="n">
-        <v>6615299</v>
+        <v>6615346</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517868</v>
+        <v>123517882</v>
       </c>
       <c r="B5" t="n">
-        <v>90966</v>
+        <v>100662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,25 +1001,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637396</v>
+        <v>637160</v>
       </c>
       <c r="R5" t="n">
-        <v>6615346</v>
+        <v>6615284</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37417-2023 artfynd.xlsx
+++ b/artfynd/A 37417-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517878</v>
+        <v>123517868</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637093</v>
+        <v>637396</v>
       </c>
       <c r="R2" t="n">
-        <v>6615299</v>
+        <v>6615346</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517839</v>
+        <v>123517882</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>100680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersta, Upl</t>
+          <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637306</v>
+        <v>637160</v>
       </c>
       <c r="R3" t="n">
-        <v>6615070</v>
+        <v>6615284</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517868</v>
+        <v>123517878</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637396</v>
+        <v>637093</v>
       </c>
       <c r="R4" t="n">
-        <v>6615346</v>
+        <v>6615299</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -957,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517882</v>
+        <v>123517839</v>
       </c>
       <c r="B5" t="n">
-        <v>100662</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,38 +997,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bälsunda, Upl</t>
+          <t>Segersta, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637160</v>
+        <v>637306</v>
       </c>
       <c r="R5" t="n">
-        <v>6615284</v>
+        <v>6615070</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 37417-2023 artfynd.xlsx
+++ b/artfynd/A 37417-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517868</v>
+        <v>123517839</v>
       </c>
       <c r="B2" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bälsunda, Upl</t>
+          <t>Segersta, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637396</v>
+        <v>637306</v>
       </c>
       <c r="R2" t="n">
-        <v>6615346</v>
+        <v>6615070</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517882</v>
+        <v>123517878</v>
       </c>
       <c r="B3" t="n">
-        <v>100680</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +793,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637160</v>
+        <v>637093</v>
       </c>
       <c r="R3" t="n">
-        <v>6615284</v>
+        <v>6615299</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517878</v>
+        <v>123517882</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>100682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,42 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637093</v>
+        <v>637160</v>
       </c>
       <c r="R4" t="n">
-        <v>6615299</v>
+        <v>6615284</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517839</v>
+        <v>123517868</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +1001,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Segersta, Upl</t>
+          <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637306</v>
+        <v>637396</v>
       </c>
       <c r="R5" t="n">
-        <v>6615070</v>
+        <v>6615346</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37417-2023 artfynd.xlsx
+++ b/artfynd/A 37417-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517839</v>
+        <v>123517882</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Segersta, Upl</t>
+          <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637306</v>
+        <v>637160</v>
       </c>
       <c r="R2" t="n">
-        <v>6615070</v>
+        <v>6615284</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -784,7 +780,7 @@
         <v>123517878</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517882</v>
+        <v>123517868</v>
       </c>
       <c r="B4" t="n">
-        <v>100682</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637160</v>
+        <v>637396</v>
       </c>
       <c r="R4" t="n">
-        <v>6615284</v>
+        <v>6615346</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -957,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517868</v>
+        <v>123517839</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,38 +997,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bälsunda, Upl</t>
+          <t>Segersta, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637396</v>
+        <v>637306</v>
       </c>
       <c r="R5" t="n">
-        <v>6615346</v>
+        <v>6615070</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37417-2023 artfynd.xlsx
+++ b/artfynd/A 37417-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517882</v>
+        <v>123517839</v>
       </c>
       <c r="B2" t="n">
-        <v>100257</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bälsunda, Upl</t>
+          <t>Segersta, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637160</v>
+        <v>637306</v>
       </c>
       <c r="R2" t="n">
-        <v>6615284</v>
+        <v>6615070</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517868</v>
+        <v>123517882</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637396</v>
+        <v>637160</v>
       </c>
       <c r="R4" t="n">
-        <v>6615346</v>
+        <v>6615284</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -953,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517839</v>
+        <v>123517868</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +1001,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Segersta, Upl</t>
+          <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637306</v>
+        <v>637396</v>
       </c>
       <c r="R5" t="n">
-        <v>6615070</v>
+        <v>6615346</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37417-2023 artfynd.xlsx
+++ b/artfynd/A 37417-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517839</v>
+        <v>123517882</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Segersta, Upl</t>
+          <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637306</v>
+        <v>637160</v>
       </c>
       <c r="R2" t="n">
-        <v>6615070</v>
+        <v>6615284</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517882</v>
+        <v>123517839</v>
       </c>
       <c r="B4" t="n">
-        <v>100257</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +895,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bälsunda, Upl</t>
+          <t>Segersta, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637160</v>
+        <v>637306</v>
       </c>
       <c r="R4" t="n">
-        <v>6615284</v>
+        <v>6615070</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 37417-2023 artfynd.xlsx
+++ b/artfynd/A 37417-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517882</v>
+        <v>123517868</v>
       </c>
       <c r="B2" t="n">
-        <v>100257</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637160</v>
+        <v>637396</v>
       </c>
       <c r="R2" t="n">
-        <v>6615284</v>
+        <v>6615346</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517878</v>
+        <v>123517882</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637093</v>
+        <v>637160</v>
       </c>
       <c r="R3" t="n">
-        <v>6615299</v>
+        <v>6615284</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -989,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517868</v>
+        <v>123517878</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,38 +997,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637396</v>
+        <v>637093</v>
       </c>
       <c r="R5" t="n">
-        <v>6615346</v>
+        <v>6615299</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37417-2023 artfynd.xlsx
+++ b/artfynd/A 37417-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517868</v>
+        <v>123517839</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bälsunda, Upl</t>
+          <t>Segersta, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637396</v>
+        <v>637306</v>
       </c>
       <c r="R2" t="n">
-        <v>6615346</v>
+        <v>6615070</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517882</v>
+        <v>123517878</v>
       </c>
       <c r="B3" t="n">
-        <v>100257</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +793,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637160</v>
+        <v>637093</v>
       </c>
       <c r="R3" t="n">
-        <v>6615284</v>
+        <v>6615299</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517839</v>
+        <v>123517882</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,42 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Segersta, Upl</t>
+          <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637306</v>
+        <v>637160</v>
       </c>
       <c r="R4" t="n">
-        <v>6615070</v>
+        <v>6615284</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517878</v>
+        <v>123517868</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +1001,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637093</v>
+        <v>637396</v>
       </c>
       <c r="R5" t="n">
-        <v>6615299</v>
+        <v>6615346</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37417-2023 artfynd.xlsx
+++ b/artfynd/A 37417-2023 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123517839</v>
+        <v>123517868</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Segersta, Upl</t>
+          <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637306</v>
+        <v>637396</v>
       </c>
       <c r="R2" t="n">
-        <v>6615070</v>
+        <v>6615346</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123517878</v>
+        <v>123517839</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,19 +802,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bälsunda, Upl</t>
+          <t>Segersta, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637093</v>
+        <v>637306</v>
       </c>
       <c r="R3" t="n">
-        <v>6615299</v>
+        <v>6615070</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,50 +873,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123517882</v>
+        <v>123517878</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bälsunda, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637160</v>
+        <v>637093</v>
       </c>
       <c r="R4" t="n">
-        <v>6615284</v>
+        <v>6615299</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,37 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123517868</v>
+        <v>123517882</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637396</v>
+        <v>637160</v>
       </c>
       <c r="R5" t="n">
-        <v>6615346</v>
+        <v>6615284</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,12 +1039,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37417-2023 artfynd.xlsx
+++ b/artfynd/A 37417-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123517868</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123517839</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123517878</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,8 +1088,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123517882</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>